--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -43390,13 +43390,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O230" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R230" t="n">
-        <v>0.3551054562747671</v>
+        <v>0.3644503367030505</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43554,10 +43554,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O231" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -44804,13 +44804,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O239" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R239" t="n">
-        <v>0.996133135683917</v>
+        <v>1.013921227392558</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44968,10 +44968,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O240" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -45207,13 +45207,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O241" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R241" t="n">
-        <v>0.8430169168495401</v>
+        <v>0.844954886773332</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -45716,12 +45716,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45746,22 +45746,22 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="O244" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="R244" t="n">
-        <v>0.3268802519372613</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45780,70 +45780,75 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45870,17 +45875,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45905,31 +45910,48 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -45937,6 +45959,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45949,7 +46029,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -45959,7 +46039,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -45967,47 +46047,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -46034,17 +46114,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46078,39 +46158,22 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="O246" t="n">
-        <v>2</v>
+        <v>89</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.3268802519372613</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -46118,135 +46181,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="AT246" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV246" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46278,12 +46278,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46317,81 +46317,100 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="O247" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="R247" t="n">
-        <v>0.05038721801859319</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46418,17 +46437,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46462,22 +46481,39 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46485,6 +46521,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46497,7 +46591,7 @@
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
@@ -46507,7 +46601,7 @@
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -46515,47 +46609,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46582,217 +46676,526 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>40</v>
+      </c>
+      <c r="O249" t="n">
+        <v>40</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.07751879695168185</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G251" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="K251" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N249" t="n">
+      <c r="N251" t="n">
         <v>0</v>
       </c>
-      <c r="O249" t="n">
+      <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="U251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
+      <c r="V251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W249" t="inlineStr">
+      <c r="W251" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X249" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y249" t="inlineStr">
+      <c r="Y251" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z249" t="inlineStr">
+      <c r="Z251" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA249" t="inlineStr">
+      <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB249" t="inlineStr">
+      <c r="AB251" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
+      <c r="AC251" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD249" t="inlineStr">
+      <c r="AD251" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE249" t="inlineStr">
+      <c r="AE251" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF249" t="inlineStr">
+      <c r="AF251" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG249" t="inlineStr">
+      <c r="AG251" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH249" t="inlineStr">
+      <c r="AH251" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI249" t="inlineStr">
+      <c r="AI251" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ249" t="inlineStr">
+      <c r="AJ251" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK249" t="inlineStr">
+      <c r="AK251" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM249" t="inlineStr">
+      <c r="AM251" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN249" t="b">
+      <c r="AN251" t="b">
         <v>1</v>
       </c>
-      <c r="AO249" t="inlineStr">
+      <c r="AO251" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP249" t="inlineStr">
+      <c r="AP251" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ249" t="inlineStr">
+      <c r="AQ251" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR249" t="inlineStr">
+      <c r="AR251" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS249" t="inlineStr">
+      <c r="AS251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT249" t="n">
+      <c r="AT251" t="n">
         <v>2</v>
       </c>
-      <c r="AU249" t="inlineStr">
+      <c r="AU251" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV249" t="inlineStr">
+      <c r="AV251" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW249" t="inlineStr">
+      <c r="AW251" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX249" t="inlineStr">
+      <c r="AX251" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY249" t="inlineStr">
+      <c r="AY251" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ249" t="inlineStr">
+      <c r="AZ251" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA249" t="inlineStr">
+      <c r="BA251" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB249" t="inlineStr">
+      <c r="BB251" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC249" t="inlineStr">
+      <c r="BC251" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -46914,7 +47317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -46924,7 +47327,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -46944,7 +47347,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -46976,7 +47379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154369</v>
+        <v>154434</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -43793,13 +43793,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O232" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="R232" t="n">
-        <v>1.557272211476391</v>
+        <v>1.560945023295911</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -45207,13 +45207,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O241" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R241" t="n">
-        <v>0.844954886773332</v>
+        <v>0.8507687965447082</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -46317,13 +46317,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O247" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -46481,10 +46481,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O248" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -46720,13 +46720,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O249" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R249" t="n">
-        <v>0.07751879695168185</v>
+        <v>0.1027124059609784</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154434</v>
+        <v>154453</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -43793,13 +43793,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O232" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="R232" t="n">
-        <v>1.560945023295911</v>
+        <v>1.549926587837352</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -44804,13 +44804,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O239" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R239" t="n">
-        <v>1.013921227392558</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44968,10 +44968,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O240" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -45207,13 +45207,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O241" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R241" t="n">
-        <v>0.8507687965447082</v>
+        <v>0.8546447363922922</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -46720,13 +46720,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="O249" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="R249" t="n">
-        <v>0.1027124059609784</v>
+        <v>0.1162781954275228</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -46865,13 +46865,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -47029,10 +47029,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154453</v>
+        <v>154467</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -41901,13 +41901,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O222" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R222" t="n">
-        <v>1.387471153274027</v>
+        <v>1.405259244982669</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -42065,10 +42065,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O223" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
@@ -43793,13 +43793,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O232" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R232" t="n">
-        <v>1.549926587837352</v>
+        <v>1.542580964198312</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -44765,12 +44765,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44804,13 +44804,16 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="O239" t="n">
-        <v>59</v>
+        <v>14501</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>228</v>
       </c>
       <c r="R239" t="n">
-        <v>1.049497410809841</v>
+        <v>1.026318593467688</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44819,7 +44822,7 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -44829,75 +44832,70 @@
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -44929,12 +44927,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44968,29 +44966,29 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="O240" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y240" t="inlineStr">
@@ -45000,7 +44998,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -45015,7 +45013,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -45030,7 +45028,7 @@
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG240" t="inlineStr">
@@ -45050,17 +45048,17 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -45068,75 +45066,70 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45168,12 +45161,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45207,81 +45200,100 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>441</v>
+        <v>59</v>
       </c>
       <c r="O241" t="n">
-        <v>441</v>
+        <v>59</v>
       </c>
       <c r="R241" t="n">
-        <v>0.8546447363922922</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45308,17 +45320,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45352,22 +45364,39 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="O242" t="n">
-        <v>27</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.4776234729647867</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>59</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -45375,6 +45404,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45387,7 +45474,7 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
@@ -45397,7 +45484,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -45405,47 +45492,47 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45472,17 +45559,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45516,175 +45603,81 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>27</v>
+        <v>441</v>
       </c>
       <c r="O243" t="n">
-        <v>27</v>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
+        <v>441</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.8546447363922922</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45716,12 +45709,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45755,13 +45748,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O244" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R244" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.4776234729647867</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -45770,7 +45763,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45800,7 +45793,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -45813,42 +45806,42 @@
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45880,12 +45873,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45919,29 +45912,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O245" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -45966,7 +45959,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -46001,17 +45994,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -46039,7 +46032,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -46052,42 +46045,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46119,12 +46112,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46149,22 +46142,22 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="O246" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="R246" t="n">
-        <v>0.3268802519372613</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -46173,7 +46166,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -46183,70 +46176,75 @@
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -46273,17 +46271,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46308,31 +46306,48 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="O247" t="n">
-        <v>11</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.1956690087950551</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -46340,6 +46355,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46352,7 +46425,7 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
@@ -46362,7 +46435,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -46370,47 +46443,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -46437,17 +46510,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46481,39 +46554,22 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="O248" t="n">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0.3268802519372613</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46521,135 +46577,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO248" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP248" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="AT248" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV248" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46681,12 +46674,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46720,81 +46713,100 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O249" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="R249" t="n">
-        <v>0.1162781954275228</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46821,17 +46833,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46865,22 +46877,39 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O250" t="n">
-        <v>6</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46888,6 +46917,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46900,7 +46987,7 @@
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
@@ -46910,7 +46997,7 @@
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT250" t="n">
@@ -46918,47 +47005,47 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46985,217 +47072,526 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>60</v>
+      </c>
+      <c r="O251" t="n">
+        <v>60</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.1162781954275228</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>6</v>
+      </c>
+      <c r="O252" t="n">
+        <v>6</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N253" t="n">
         <v>6</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O253" t="n">
         <v>6</v>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="U253" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
+      <c r="V253" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W251" t="inlineStr">
+      <c r="W253" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y251" t="inlineStr">
+      <c r="Y253" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
+      <c r="Z253" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA251" t="inlineStr">
+      <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
+      <c r="AB253" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
+      <c r="AC253" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD251" t="inlineStr">
+      <c r="AD253" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE251" t="inlineStr">
+      <c r="AE253" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF251" t="inlineStr">
+      <c r="AF253" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG251" t="inlineStr">
+      <c r="AG253" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH251" t="inlineStr">
+      <c r="AH253" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI251" t="inlineStr">
+      <c r="AI253" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ251" t="inlineStr">
+      <c r="AJ253" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK251" t="inlineStr">
+      <c r="AK253" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM251" t="inlineStr">
+      <c r="AM253" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN251" t="b">
+      <c r="AN253" t="b">
         <v>1</v>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO253" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP253" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ251" t="inlineStr">
+      <c r="AQ253" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
+      <c r="AR253" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr">
+      <c r="AS253" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT251" t="n">
+      <c r="AT253" t="n">
         <v>2</v>
       </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AU253" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV253" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW253" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX253" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY253" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ253" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA253" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB253" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC253" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47317,7 +47713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -47327,7 +47723,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -47347,7 +47743,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -47379,7 +47775,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154467</v>
+        <v>168972</v>
       </c>
     </row>
     <row r="16">
@@ -47389,7 +47785,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>962</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O2" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O3" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O66" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O67" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -18546,10 +18546,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="O96" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18702,10 +18702,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="O97" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -24215,10 +24215,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O126" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24371,10 +24371,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O127" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -31514,10 +31514,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O166" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -31670,10 +31670,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O167" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
@@ -38386,12 +38386,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38425,25 +38425,19 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>15974</v>
+        <v>258</v>
       </c>
       <c r="O204" t="n">
-        <v>15974</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>249</v>
-      </c>
-      <c r="R204" t="n">
-        <v>1.130571216609395</v>
+        <v>258</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -38453,7 +38447,7 @@
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
@@ -38463,12 +38457,12 @@
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
@@ -38476,47 +38470,47 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38548,12 +38542,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38587,29 +38581,29 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>15974</v>
+        <v>258</v>
       </c>
       <c r="O205" t="n">
-        <v>15974</v>
+        <v>258</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>SRC_CN_CDC</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y205" t="inlineStr">
@@ -38634,7 +38628,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>country:CN:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -38649,7 +38643,7 @@
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG205" t="inlineStr">
@@ -38669,17 +38663,17 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
+          <t>PHO IDTO current-year monthly preliminary hepatitis C notifications without an acute/chronic source split; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -38687,7 +38681,7 @@
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
@@ -38697,12 +38691,12 @@
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -38710,47 +38704,47 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38782,12 +38776,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38821,14 +38815,25 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>524</v>
+        <v>15974</v>
       </c>
       <c r="O206" t="n">
-        <v>524</v>
+        <v>15974</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>249</v>
+      </c>
+      <c r="R206" t="n">
+        <v>1.130571216609395</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -38838,70 +38843,70 @@
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -38933,12 +38938,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38972,24 +38977,24 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>524</v>
+        <v>15974</v>
       </c>
       <c r="O207" t="n">
-        <v>524</v>
+        <v>15974</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
@@ -39004,7 +39009,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -39019,7 +39024,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>country:CN-AH:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -39034,7 +39039,7 @@
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
@@ -39054,12 +39059,12 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -39072,70 +39077,70 @@
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -39167,12 +39172,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -39206,10 +39211,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>375</v>
+        <v>524</v>
       </c>
       <c r="O208" t="n">
-        <v>375</v>
+        <v>524</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -39281,7 +39286,7 @@
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
@@ -39318,12 +39323,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -39357,10 +39362,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>375</v>
+        <v>524</v>
       </c>
       <c r="O209" t="n">
-        <v>375</v>
+        <v>524</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -39404,7 +39409,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -39515,7 +39520,7 @@
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
@@ -39552,12 +39557,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -39591,10 +39596,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>1945</v>
+        <v>375</v>
       </c>
       <c r="O210" t="n">
-        <v>1945</v>
+        <v>375</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -39666,7 +39671,7 @@
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
@@ -39703,12 +39708,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39742,10 +39747,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1945</v>
+        <v>375</v>
       </c>
       <c r="O211" t="n">
-        <v>1945</v>
+        <v>375</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -39789,7 +39794,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -39900,7 +39905,7 @@
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -39937,12 +39942,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39976,10 +39981,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="O212" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -40051,7 +40056,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -40088,12 +40093,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -40127,10 +40132,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="O213" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -40174,7 +40179,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -40285,7 +40290,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -40322,12 +40327,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -40361,10 +40366,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="O214" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -40436,7 +40441,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -40473,12 +40478,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40512,10 +40517,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="O215" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -40559,7 +40564,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -40670,7 +40675,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -40707,12 +40712,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40746,10 +40751,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="O216" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -40821,7 +40826,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -40858,12 +40863,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40897,10 +40902,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="O217" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -40944,7 +40949,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -41055,7 +41060,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -41092,12 +41097,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -41131,10 +41136,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="O218" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -41206,7 +41211,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -41243,12 +41248,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -41282,10 +41287,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="O219" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -41329,7 +41334,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -41440,7 +41445,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -41477,12 +41482,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -41516,10 +41521,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="O220" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -41591,7 +41596,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -41628,12 +41633,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -41667,10 +41672,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="O221" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -41714,7 +41719,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -41825,7 +41830,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -41862,12 +41867,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -41901,22 +41906,14 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>79</v>
-      </c>
-      <c r="R222" t="n">
-        <v>1.405259244982669</v>
+        <v>1</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -41931,22 +41928,17 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -41954,47 +41946,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -42026,12 +42018,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -42065,29 +42057,29 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -42097,7 +42089,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -42112,7 +42104,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -42147,17 +42139,17 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -42170,22 +42162,17 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -42193,47 +42180,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -42265,12 +42252,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -42304,81 +42291,100 @@
         </is>
       </c>
       <c r="N224" t="n">
+        <v>79</v>
+      </c>
+      <c r="O224" t="n">
+        <v>79</v>
+      </c>
+      <c r="R224" t="n">
+        <v>1.405259244982669</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
         <v>2</v>
       </c>
-      <c r="O224" t="n">
-        <v>2</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.02710540560393419</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP224" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
-      <c r="AT224" t="n">
-        <v>0</v>
-      </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42405,17 +42411,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -42449,81 +42455,175 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="O225" t="n">
-        <v>446</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.8643345860112523</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>79</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42555,12 +42655,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42594,100 +42694,81 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R226" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -42714,17 +42795,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42758,175 +42839,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="O227" t="n">
-        <v>21</v>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
+        <v>446</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.8643345860112523</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42958,12 +42945,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42997,13 +42984,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="O228" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="R228" t="n">
-        <v>0.132388232653028</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -43012,7 +42999,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -43027,7 +43014,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -43035,57 +43022,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43117,12 +43109,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -43156,29 +43148,29 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="O229" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -43188,7 +43180,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -43203,7 +43195,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -43238,17 +43230,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -43261,7 +43253,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
@@ -43269,57 +43261,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43351,12 +43348,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43390,13 +43387,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="O230" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="R230" t="n">
-        <v>0.3644503367030505</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43405,7 +43402,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -43420,7 +43417,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -43428,62 +43425,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43515,12 +43507,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -43554,29 +43546,29 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="O231" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -43586,7 +43578,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -43601,7 +43593,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -43636,17 +43628,17 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -43659,7 +43651,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -43667,62 +43659,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43754,12 +43741,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43784,22 +43771,22 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>420</v>
+        <v>39</v>
       </c>
       <c r="O232" t="n">
-        <v>420</v>
+        <v>39</v>
       </c>
       <c r="R232" t="n">
-        <v>1.542580964198312</v>
+        <v>0.3644503367030505</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -43808,7 +43795,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -43818,70 +43805,75 @@
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43908,17 +43900,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -43943,87 +43935,184 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="O233" t="n">
-        <v>12</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44055,12 +44144,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -44094,38 +44183,55 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>62</v>
+        <v>420</v>
       </c>
       <c r="O234" t="n">
-        <v>62</v>
+        <v>420</v>
+      </c>
+      <c r="R234" t="n">
+        <v>1.542580964198312</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -44135,12 +44241,12 @@
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -44155,12 +44261,12 @@
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
@@ -44197,12 +44303,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44236,10 +44342,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="O235" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -44277,7 +44383,7 @@
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
@@ -44297,7 +44403,7 @@
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
@@ -44339,12 +44445,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44378,10 +44484,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="O236" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -44419,7 +44525,7 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
@@ -44439,7 +44545,7 @@
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
@@ -44481,12 +44587,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44520,10 +44626,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="O237" t="n">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44561,7 +44667,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -44581,7 +44687,7 @@
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
@@ -44623,12 +44729,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44662,10 +44768,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="O238" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -44703,7 +44809,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -44723,7 +44829,7 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
@@ -44765,12 +44871,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44804,98 +44910,78 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>14501</v>
+        <v>90</v>
       </c>
       <c r="O239" t="n">
-        <v>14501</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>228</v>
-      </c>
-      <c r="R239" t="n">
-        <v>1.026318593467688</v>
+        <v>90</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44922,17 +45008,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44966,170 +45052,78 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>14501</v>
+        <v>71</v>
       </c>
       <c r="O240" t="n">
-        <v>14501</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_CN_CDC</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>丙型肝炎</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:CN:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
+        <v>71</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AT240" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV240" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45161,12 +45155,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45200,13 +45194,16 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="O241" t="n">
-        <v>59</v>
+        <v>14501</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>228</v>
       </c>
       <c r="R241" t="n">
-        <v>1.049497410809841</v>
+        <v>1.026318593467688</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -45215,7 +45212,7 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -45225,75 +45222,70 @@
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45325,12 +45317,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45364,29 +45356,29 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="O242" t="n">
-        <v>59</v>
+        <v>14501</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y242" t="inlineStr">
@@ -45396,7 +45388,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -45411,7 +45403,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -45426,7 +45418,7 @@
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG242" t="inlineStr">
@@ -45446,17 +45438,17 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -45464,75 +45456,70 @@
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45564,12 +45551,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45603,81 +45590,100 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>441</v>
+        <v>59</v>
       </c>
       <c r="O243" t="n">
-        <v>441</v>
+        <v>59</v>
       </c>
       <c r="R243" t="n">
-        <v>0.8546447363922922</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45704,17 +45710,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45748,22 +45754,39 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="O244" t="n">
-        <v>27</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.4776234729647867</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>59</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45771,6 +45794,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45783,7 +45864,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -45793,7 +45874,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -45801,47 +45882,47 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45868,17 +45949,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45912,175 +45993,81 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>27</v>
+        <v>441</v>
       </c>
       <c r="O245" t="n">
-        <v>27</v>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
+        <v>441</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.8546447363922922</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46112,12 +46099,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46151,13 +46138,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O246" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R246" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.4776234729647867</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -46166,7 +46153,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -46196,7 +46183,7 @@
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -46209,42 +46196,42 @@
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46276,12 +46263,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46315,29 +46302,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O247" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -46362,7 +46349,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -46397,17 +46384,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -46435,7 +46422,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -46448,42 +46435,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46515,12 +46502,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46545,22 +46532,22 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="O248" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="R248" t="n">
-        <v>0.3268802519372613</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -46569,7 +46556,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46579,70 +46566,75 @@
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -46669,17 +46661,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46704,31 +46696,48 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N249" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="O249" t="n">
-        <v>16</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.284609467338262</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -46736,6 +46745,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46748,7 +46815,7 @@
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
@@ -46758,7 +46825,7 @@
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -46766,47 +46833,47 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -46833,17 +46900,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46877,39 +46944,22 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="O250" t="n">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.3268802519372613</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46917,135 +46967,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP250" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="AT250" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU250" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV250" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47077,12 +47064,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -47116,81 +47103,100 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O251" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="R251" t="n">
-        <v>0.1162781954275228</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47217,17 +47223,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47261,22 +47267,39 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O252" t="n">
-        <v>6</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47284,6 +47307,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47296,7 +47377,7 @@
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
@@ -47306,7 +47387,7 @@
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT252" t="n">
@@ -47314,47 +47395,47 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47381,217 +47462,526 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>60</v>
+      </c>
+      <c r="O253" t="n">
+        <v>60</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.1162781954275228</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>6</v>
+      </c>
+      <c r="O254" t="n">
+        <v>6</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G255" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="K255" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="L255" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N253" t="n">
+      <c r="N255" t="n">
         <v>6</v>
       </c>
-      <c r="O253" t="n">
+      <c r="O255" t="n">
         <v>6</v>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="U255" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
+      <c r="V255" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W253" t="inlineStr">
+      <c r="W255" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y253" t="inlineStr">
+      <c r="Y255" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z253" t="inlineStr">
+      <c r="Z255" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA253" t="inlineStr">
+      <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB253" t="inlineStr">
+      <c r="AB255" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC253" t="inlineStr">
+      <c r="AC255" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD253" t="inlineStr">
+      <c r="AD255" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE253" t="inlineStr">
+      <c r="AE255" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF253" t="inlineStr">
+      <c r="AF255" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG253" t="inlineStr">
+      <c r="AG255" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH253" t="inlineStr">
+      <c r="AH255" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI253" t="inlineStr">
+      <c r="AI255" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ253" t="inlineStr">
+      <c r="AJ255" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK253" t="inlineStr">
+      <c r="AK255" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM253" t="inlineStr">
+      <c r="AM255" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN253" t="b">
+      <c r="AN255" t="b">
         <v>1</v>
       </c>
-      <c r="AO253" t="inlineStr">
+      <c r="AO255" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP253" t="inlineStr">
+      <c r="AP255" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ253" t="inlineStr">
+      <c r="AQ255" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR253" t="inlineStr">
+      <c r="AR255" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS253" t="inlineStr">
+      <c r="AS255" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT253" t="n">
+      <c r="AT255" t="n">
         <v>2</v>
       </c>
-      <c r="AU253" t="inlineStr">
+      <c r="AU255" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV253" t="inlineStr">
+      <c r="AV255" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW253" t="inlineStr">
+      <c r="AW255" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX253" t="inlineStr">
+      <c r="AX255" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY253" t="inlineStr">
+      <c r="AY255" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ253" t="inlineStr">
+      <c r="AZ255" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA253" t="inlineStr">
+      <c r="BA255" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB253" t="inlineStr">
+      <c r="BB255" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC253" t="inlineStr">
+      <c r="BC255" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47713,7 +48103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -47723,7 +48113,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -47743,7 +48133,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -47775,7 +48165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168972</v>
+        <v>169236</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -44183,13 +44183,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O234" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="R234" t="n">
-        <v>1.542580964198312</v>
+        <v>1.538908152378792</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -45590,13 +45590,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O243" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R243" t="n">
-        <v>1.049497410809841</v>
+        <v>1.067285502518482</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -45754,10 +45754,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O244" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -45993,13 +45993,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O245" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="R245" t="n">
-        <v>0.8546447363922922</v>
+        <v>0.8565827063160842</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -47103,13 +47103,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O251" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R251" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -47267,10 +47267,10 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O252" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
@@ -47506,13 +47506,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="O253" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="R253" t="n">
-        <v>0.1162781954275228</v>
+        <v>0.2228665412360853</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169236</v>
+        <v>169296</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -44183,13 +44183,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>419</v>
+        <v>340</v>
       </c>
       <c r="O234" t="n">
-        <v>419</v>
+        <v>340</v>
       </c>
       <c r="R234" t="n">
-        <v>1.538908152378792</v>
+        <v>1.248756018636729</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169296</v>
+        <v>169217</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -47103,13 +47103,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O251" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R251" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.4802784761333171</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -47267,10 +47267,10 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O252" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
@@ -47506,13 +47506,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="O253" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="R253" t="n">
-        <v>0.2228665412360853</v>
+        <v>0.2441842103977978</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169217</v>
+        <v>169235</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -43387,13 +43387,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O230" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R230" t="n">
-        <v>0.132388232653028</v>
+        <v>0.05673781399415487</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43546,10 +43546,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O231" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -46502,12 +46502,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46541,13 +46541,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="O248" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="R248" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.2836890699707744</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46571,7 +46571,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -46579,62 +46579,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46666,12 +46661,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46705,29 +46700,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="O249" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -46737,7 +46732,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -46752,7 +46747,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -46787,17 +46782,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -46810,7 +46805,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -46818,62 +46813,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46905,12 +46895,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46935,22 +46925,22 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N250" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="O250" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="R250" t="n">
-        <v>0.3268802519372613</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -46959,7 +46949,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46969,70 +46959,75 @@
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47059,17 +47054,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -47094,31 +47089,48 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O251" t="n">
-        <v>27</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.4802784761333171</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -47126,6 +47138,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47138,7 +47208,7 @@
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
@@ -47148,7 +47218,7 @@
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -47156,47 +47226,47 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47223,17 +47293,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47267,39 +47337,22 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="O252" t="n">
-        <v>27</v>
+        <v>89</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.3268802519372613</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47307,135 +47360,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN252" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="AT252" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV252" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47467,12 +47457,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -47506,81 +47496,100 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="O253" t="n">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="R253" t="n">
-        <v>0.2441842103977978</v>
+        <v>0.4802784761333171</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47607,17 +47616,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -47651,22 +47660,39 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="O254" t="n">
-        <v>6</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -47674,6 +47700,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47686,7 +47770,7 @@
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
@@ -47696,7 +47780,7 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT254" t="n">
@@ -47704,47 +47788,47 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47771,217 +47855,526 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>138</v>
+      </c>
+      <c r="O255" t="n">
+        <v>138</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.2674398494833023</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>6</v>
+      </c>
+      <c r="O256" t="n">
+        <v>6</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="K257" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="L257" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N255" t="n">
+      <c r="N257" t="n">
         <v>6</v>
       </c>
-      <c r="O255" t="n">
+      <c r="O257" t="n">
         <v>6</v>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="U257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
+      <c r="V257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W255" t="inlineStr">
+      <c r="W257" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y255" t="inlineStr">
+      <c r="Y257" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr">
+      <c r="Z257" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA255" t="inlineStr">
+      <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
+      <c r="AB257" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC255" t="inlineStr">
+      <c r="AC257" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD255" t="inlineStr">
+      <c r="AD257" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE255" t="inlineStr">
+      <c r="AE257" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF255" t="inlineStr">
+      <c r="AF257" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG255" t="inlineStr">
+      <c r="AG257" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH255" t="inlineStr">
+      <c r="AH257" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI255" t="inlineStr">
+      <c r="AI257" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ255" t="inlineStr">
+      <c r="AJ257" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK255" t="inlineStr">
+      <c r="AK257" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM255" t="inlineStr">
+      <c r="AM257" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN255" t="b">
+      <c r="AN257" t="b">
         <v>1</v>
       </c>
-      <c r="AO255" t="inlineStr">
+      <c r="AO257" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP255" t="inlineStr">
+      <c r="AP257" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ255" t="inlineStr">
+      <c r="AQ257" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR255" t="inlineStr">
+      <c r="AR257" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS255" t="inlineStr">
+      <c r="AS257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT255" t="n">
+      <c r="AT257" t="n">
         <v>2</v>
       </c>
-      <c r="AU255" t="inlineStr">
+      <c r="AU257" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV255" t="inlineStr">
+      <c r="AV257" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW255" t="inlineStr">
+      <c r="AW257" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX255" t="inlineStr">
+      <c r="AX257" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY255" t="inlineStr">
+      <c r="AY257" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ255" t="inlineStr">
+      <c r="AZ257" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA255" t="inlineStr">
+      <c r="BA257" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB255" t="inlineStr">
+      <c r="BB257" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC255" t="inlineStr">
+      <c r="BC257" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48103,7 +48496,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -48113,7 +48506,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -48133,7 +48526,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -48165,7 +48558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169235</v>
+        <v>169258</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -46138,13 +46138,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O246" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R246" t="n">
-        <v>0.4776234729647867</v>
+        <v>0.4953132312227418</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -46302,10 +46302,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O247" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -48044,13 +48044,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O256" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R256" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -48208,10 +48208,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O257" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169258</v>
+        <v>169265</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -42291,13 +42291,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O224" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R224" t="n">
-        <v>1.405259244982669</v>
+        <v>1.42304733669131</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -42455,10 +42455,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O225" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -45590,13 +45590,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O243" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R243" t="n">
-        <v>1.067285502518482</v>
+        <v>1.085073594227124</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -45754,10 +45754,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O244" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -47496,13 +47496,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="O253" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R253" t="n">
-        <v>0.4802784761333171</v>
+        <v>0.6225832098024481</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -47660,10 +47660,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="O254" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169265</v>
+        <v>169275</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -44183,13 +44183,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O234" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="R234" t="n">
-        <v>1.248756018636729</v>
+        <v>1.259774454095288</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -47899,13 +47899,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="O255" t="n">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="R255" t="n">
-        <v>0.2674398494833023</v>
+        <v>0.4050357140725376</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169275</v>
+        <v>169349</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -44183,13 +44183,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O234" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R234" t="n">
-        <v>1.259774454095288</v>
+        <v>1.263447265914808</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -45993,13 +45993,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="O245" t="n">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="R245" t="n">
-        <v>0.8565827063160842</v>
+        <v>0.8798383454015888</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -47899,13 +47899,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="O255" t="n">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="R255" t="n">
-        <v>0.4050357140725376</v>
+        <v>0.4961203004907638</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169349</v>
+        <v>169409</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -30510,7 +30510,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35549,13 +35549,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R187" t="n">
-        <v>0.06776351400983546</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -39059,7 +39059,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -44183,13 +44183,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>344</v>
+        <v>419</v>
       </c>
       <c r="O234" t="n">
-        <v>344</v>
+        <v>419</v>
       </c>
       <c r="R234" t="n">
-        <v>1.263447265914808</v>
+        <v>1.538908152378792</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -45954,12 +45954,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45993,13 +45993,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>454</v>
+        <v>3</v>
       </c>
       <c r="O245" t="n">
-        <v>454</v>
+        <v>3</v>
       </c>
       <c r="R245" t="n">
-        <v>0.8798383454015888</v>
+        <v>0.04065810840590128</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -46032,42 +46032,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46099,12 +46099,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46138,100 +46138,81 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>28</v>
+        <v>452</v>
       </c>
       <c r="O246" t="n">
-        <v>28</v>
+        <v>452</v>
       </c>
       <c r="R246" t="n">
-        <v>0.4953132312227418</v>
+        <v>0.8759624055540047</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46258,7 +46239,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -46307,98 +46288,23 @@
       <c r="O247" t="n">
         <v>28</v>
       </c>
+      <c r="R247" t="n">
+        <v>0.4953132312227418</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U247" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -46497,17 +46403,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46541,22 +46447,39 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="O248" t="n">
-        <v>15</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.2836890699707744</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46564,6 +46487,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46571,7 +46552,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -46579,57 +46560,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46656,7 +46642,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -46705,98 +46691,23 @@
       <c r="O249" t="n">
         <v>15</v>
       </c>
+      <c r="R249" t="n">
+        <v>0.2836890699707744</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -46890,17 +46801,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46934,22 +46845,39 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="O250" t="n">
-        <v>41</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.3831400975596171</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46957,6 +46885,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46964,7 +46950,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -46972,62 +46958,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47054,7 +47035,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -47103,98 +47084,23 @@
       <c r="O251" t="n">
         <v>41</v>
       </c>
+      <c r="R251" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Hepatit C</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -47293,17 +47199,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47328,31 +47234,48 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N252" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="O252" t="n">
-        <v>89</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.3268802519372613</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47360,72 +47283,135 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47457,12 +47443,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -47496,13 +47482,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="O253" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="R253" t="n">
-        <v>0.6225832098024481</v>
+        <v>0.3268802519372613</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -47511,7 +47497,7 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -47521,75 +47507,70 @@
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47616,7 +47597,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -47660,103 +47641,28 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="O254" t="n">
-        <v>35</v>
+        <v>58</v>
+      </c>
+      <c r="R254" t="n">
+        <v>1.0317093191012</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN254" t="b">
-        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
@@ -47855,17 +47761,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -47899,81 +47805,175 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="O255" t="n">
-        <v>256</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0.4961203004907638</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>58</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48005,12 +48005,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -48044,100 +48044,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>12</v>
+        <v>314</v>
       </c>
       <c r="O256" t="n">
-        <v>12</v>
+        <v>314</v>
       </c>
       <c r="R256" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.6085225560707025</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48164,7 +48145,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -48208,103 +48189,28 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O257" t="n">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.2653463738693259</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -48375,6 +48281,245 @@
         </is>
       </c>
       <c r="BC257" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>15</v>
+      </c>
+      <c r="O258" t="n">
+        <v>15</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48496,7 +48641,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -48506,7 +48651,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -48558,7 +48703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169409</v>
+        <v>169568</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -39942,12 +39942,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39981,10 +39981,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>1945</v>
+        <v>135</v>
       </c>
       <c r="O212" t="n">
-        <v>1945</v>
+        <v>135</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -40093,12 +40093,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -40132,10 +40132,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1945</v>
+        <v>135</v>
       </c>
       <c r="O213" t="n">
-        <v>1945</v>
+        <v>135</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -40290,7 +40290,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -40327,12 +40327,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -40366,10 +40366,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="O214" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -40478,12 +40478,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40517,10 +40517,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="O215" t="n">
-        <v>857</v>
+        <v>1945</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -40675,7 +40675,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -40712,12 +40712,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40751,10 +40751,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="O216" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -40863,12 +40863,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40902,10 +40902,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="O217" t="n">
-        <v>567</v>
+        <v>857</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -41060,7 +41060,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -41097,12 +41097,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -41136,10 +41136,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="O218" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -41248,12 +41248,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -41287,10 +41287,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="O219" t="n">
-        <v>697</v>
+        <v>567</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -41445,7 +41445,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -41482,12 +41482,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -41521,10 +41521,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="O220" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -41633,12 +41633,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -41672,10 +41672,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="O221" t="n">
-        <v>1562</v>
+        <v>697</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -41830,7 +41830,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -41867,12 +41867,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -41906,10 +41906,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="O222" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -42018,12 +42018,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -42057,10 +42057,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="O223" t="n">
-        <v>1</v>
+        <v>1562</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -42215,7 +42215,7 @@
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
@@ -42252,12 +42252,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -42291,22 +42291,14 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>80</v>
-      </c>
-      <c r="R224" t="n">
-        <v>1.42304733669131</v>
+        <v>1</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -42321,22 +42313,17 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -42344,47 +42331,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -42416,12 +42403,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -42455,29 +42442,29 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -42487,7 +42474,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -42502,7 +42489,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -42537,17 +42524,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -42560,22 +42547,17 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -42583,47 +42565,47 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -42655,12 +42637,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -42694,81 +42676,100 @@
         </is>
       </c>
       <c r="N226" t="n">
+        <v>80</v>
+      </c>
+      <c r="O226" t="n">
+        <v>80</v>
+      </c>
+      <c r="R226" t="n">
+        <v>1.42304733669131</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
         <v>2</v>
       </c>
-      <c r="O226" t="n">
-        <v>2</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.02710540560393419</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
-      <c r="AT226" t="n">
-        <v>0</v>
-      </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42795,17 +42796,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42839,81 +42840,175 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="O227" t="n">
-        <v>446</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0.8643345860112523</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42945,12 +43040,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -42984,100 +43079,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O228" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R228" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43104,17 +43180,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -43148,175 +43224,81 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="O229" t="n">
-        <v>21</v>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
+        <v>446</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0.8643345860112523</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43348,12 +43330,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -43387,13 +43369,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="O230" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="R230" t="n">
-        <v>0.05673781399415487</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43402,7 +43384,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -43417,7 +43399,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -43425,57 +43407,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43507,12 +43494,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -43546,29 +43533,29 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="O231" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -43578,7 +43565,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -43593,7 +43580,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -43628,17 +43615,17 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -43651,7 +43638,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -43659,57 +43646,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43741,12 +43733,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -43780,13 +43772,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="O232" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="R232" t="n">
-        <v>0.3644503367030505</v>
+        <v>0.05673781399415487</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -43795,7 +43787,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -43810,7 +43802,7 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
@@ -43818,62 +43810,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43905,12 +43892,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -43944,29 +43931,29 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="O233" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -43976,7 +43963,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -43991,7 +43978,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -44026,17 +44013,17 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -44049,7 +44036,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
@@ -44057,62 +44044,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44144,12 +44126,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -44174,22 +44156,22 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N234" t="n">
-        <v>419</v>
+        <v>39</v>
       </c>
       <c r="O234" t="n">
-        <v>419</v>
+        <v>39</v>
       </c>
       <c r="R234" t="n">
-        <v>1.538908152378792</v>
+        <v>0.3644503367030505</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -44198,7 +44180,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -44208,70 +44190,75 @@
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44298,17 +44285,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -44333,87 +44320,184 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="O235" t="n">
-        <v>12</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44445,12 +44529,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -44484,38 +44568,55 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>62</v>
+        <v>419</v>
       </c>
       <c r="O236" t="n">
-        <v>62</v>
+        <v>419</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1.538908152378792</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -44525,12 +44626,12 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -44545,12 +44646,12 @@
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
@@ -44587,12 +44688,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44626,10 +44727,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="O237" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44667,7 +44768,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -44687,7 +44788,7 @@
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
@@ -44729,12 +44830,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44768,10 +44869,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="O238" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -44809,7 +44910,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -44829,7 +44930,7 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
@@ -44871,12 +44972,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -44910,10 +45011,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="O239" t="n">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44951,7 +45052,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -44971,7 +45072,7 @@
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
@@ -45013,12 +45114,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -45052,10 +45153,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="O240" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -45093,7 +45194,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -45113,7 +45214,7 @@
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
@@ -45155,12 +45256,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45194,98 +45295,78 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>14501</v>
+        <v>90</v>
       </c>
       <c r="O241" t="n">
-        <v>14501</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>228</v>
-      </c>
-      <c r="R241" t="n">
-        <v>1.026318593467688</v>
+        <v>90</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45312,17 +45393,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45356,170 +45437,78 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>14501</v>
+        <v>71</v>
       </c>
       <c r="O242" t="n">
-        <v>14501</v>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_CN_CDC</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>丙型肝炎</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:CN:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
+        <v>71</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
-        </is>
-      </c>
-      <c r="AT242" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV242" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45551,12 +45540,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -45590,13 +45579,16 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>61</v>
+        <v>14501</v>
       </c>
       <c r="O243" t="n">
-        <v>61</v>
+        <v>14501</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>228</v>
       </c>
       <c r="R243" t="n">
-        <v>1.085073594227124</v>
+        <v>1.026318593467688</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -45605,7 +45597,7 @@
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -45615,75 +45607,70 @@
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45715,12 +45702,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45754,29 +45741,29 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>61</v>
+        <v>14501</v>
       </c>
       <c r="O244" t="n">
-        <v>61</v>
+        <v>14501</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X244" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y244" t="inlineStr">
@@ -45786,7 +45773,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45801,7 +45788,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -45816,7 +45803,7 @@
       </c>
       <c r="AF244" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG244" t="inlineStr">
@@ -45836,17 +45823,17 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
         </is>
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -45854,75 +45841,70 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45954,12 +45936,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -45993,81 +45975,87 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3</v>
+        <v>304</v>
       </c>
       <c r="O245" t="n">
-        <v>3</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.04065810840590128</v>
+        <v>304</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46094,17 +46082,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46138,81 +46126,170 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>452</v>
+        <v>304</v>
       </c>
       <c r="O246" t="n">
-        <v>452</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.8759624055540047</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>304</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46244,12 +46321,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46283,22 +46360,14 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>28</v>
+        <v>1855</v>
       </c>
       <c r="O247" t="n">
-        <v>28</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.4953132312227418</v>
+        <v>1855</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -46313,7 +46382,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
@@ -46321,14 +46390,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -46336,47 +46400,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46408,12 +46472,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46447,29 +46511,29 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>28</v>
+        <v>1855</v>
       </c>
       <c r="O248" t="n">
-        <v>28</v>
+        <v>1855</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>Hepatitt C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -46479,7 +46543,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -46494,7 +46558,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -46529,17 +46593,17 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -46552,7 +46616,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -46560,14 +46624,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -46575,47 +46634,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46647,12 +46706,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46686,22 +46745,14 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>15</v>
+        <v>743</v>
       </c>
       <c r="O249" t="n">
-        <v>15</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.2836890699707744</v>
+        <v>743</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -46716,7 +46767,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -46726,55 +46777,55 @@
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46806,12 +46857,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -46845,29 +46896,29 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>15</v>
+        <v>743</v>
       </c>
       <c r="O250" t="n">
-        <v>15</v>
+        <v>743</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X250" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y250" t="inlineStr">
@@ -46877,7 +46928,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -46892,7 +46943,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -46927,17 +46978,17 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -46950,7 +47001,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -46960,55 +47011,55 @@
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47040,12 +47091,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -47079,22 +47130,14 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>41</v>
+        <v>497</v>
       </c>
       <c r="O251" t="n">
-        <v>41</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.3831400975596171</v>
+        <v>497</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -47109,7 +47152,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -47117,14 +47160,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -47132,47 +47170,47 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47204,12 +47242,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47243,29 +47281,29 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>41</v>
+        <v>497</v>
       </c>
       <c r="O252" t="n">
-        <v>41</v>
+        <v>497</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X252" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y252" t="inlineStr">
@@ -47275,7 +47313,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -47290,7 +47328,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -47325,17 +47363,17 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -47348,7 +47386,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -47356,14 +47394,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT252" t="n">
@@ -47371,47 +47404,47 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47443,12 +47476,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -47473,31 +47506,23 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N253" t="n">
-        <v>89</v>
+        <v>527</v>
       </c>
       <c r="O253" t="n">
-        <v>89</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.3268802519372613</v>
+        <v>527</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -47507,70 +47532,70 @@
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47597,17 +47622,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -47632,31 +47657,48 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N254" t="n">
-        <v>58</v>
+        <v>527</v>
       </c>
       <c r="O254" t="n">
-        <v>58</v>
-      </c>
-      <c r="R254" t="n">
-        <v>1.0317093191012</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>527</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -47664,6 +47706,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47671,22 +47771,17 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT254" t="n">
@@ -47694,47 +47789,47 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47761,17 +47856,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -47796,48 +47891,23 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N255" t="n">
-        <v>58</v>
+        <v>1454</v>
       </c>
       <c r="O255" t="n">
-        <v>58</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1454</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -47845,64 +47915,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
-      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47910,22 +47922,17 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT255" t="n">
@@ -47933,47 +47940,47 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48000,17 +48007,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -48035,90 +48042,179 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>314</v>
+        <v>1454</v>
       </c>
       <c r="O256" t="n">
-        <v>314</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.6085225560707025</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1454</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48150,12 +48246,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -48180,31 +48276,23 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>15</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.2653463738693259</v>
+        <v>0</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -48219,7 +48307,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
@@ -48227,14 +48315,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -48242,47 +48325,47 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48314,12 +48397,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -48344,38 +48427,38 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>Hepatitt C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
@@ -48385,7 +48468,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -48400,7 +48483,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -48435,17 +48518,17 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -48458,7 +48541,7 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
@@ -48466,14 +48549,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HEPATITIS_C; SER_CN_PROV_REPORT_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT258" t="n">
@@ -48481,45 +48559,3047 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>61</v>
+      </c>
+      <c r="O259" t="n">
+        <v>61</v>
+      </c>
+      <c r="R259" t="n">
+        <v>1.085073594227124</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>61</v>
+      </c>
+      <c r="O260" t="n">
+        <v>61</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV260" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA260" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB260" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>3</v>
+      </c>
+      <c r="O261" t="n">
+        <v>3</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0.04065810840590128</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
+      <c r="AT261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>452</v>
+      </c>
+      <c r="O262" t="n">
+        <v>452</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.8759624055540047</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
+      <c r="AT262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>28</v>
+      </c>
+      <c r="O263" t="n">
+        <v>28</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.4953132312227418</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV258" t="inlineStr">
+      <c r="AV263" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW258" t="inlineStr">
+      <c r="AW263" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX258" t="inlineStr">
+      <c r="AX263" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY258" t="inlineStr">
+      <c r="AY263" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ258" t="inlineStr">
+      <c r="AZ263" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA258" t="inlineStr">
+      <c r="BA263" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB258" t="inlineStr">
+      <c r="BB263" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC258" t="inlineStr">
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>28</v>
+      </c>
+      <c r="O264" t="n">
+        <v>28</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>15</v>
+      </c>
+      <c r="O265" t="n">
+        <v>15</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0.2836890699707744</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>15</v>
+      </c>
+      <c r="O266" t="n">
+        <v>15</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>41</v>
+      </c>
+      <c r="O267" t="n">
+        <v>41</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>41</v>
+      </c>
+      <c r="O268" t="n">
+        <v>41</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN268" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>89</v>
+      </c>
+      <c r="O269" t="n">
+        <v>89</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0.3268802519372613</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>58</v>
+      </c>
+      <c r="O270" t="n">
+        <v>58</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1.0317093191012</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>58</v>
+      </c>
+      <c r="O271" t="n">
+        <v>58</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>314</v>
+      </c>
+      <c r="O272" t="n">
+        <v>314</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.6085225560707025</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>15</v>
+      </c>
+      <c r="O273" t="n">
+        <v>15</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0.2653463738693259</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>15</v>
+      </c>
+      <c r="O274" t="n">
+        <v>15</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48641,7 +51721,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
@@ -48651,7 +51731,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -48671,7 +51751,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -48703,7 +51783,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169568</v>
+        <v>175083</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -44568,13 +44568,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>419</v>
+        <v>342</v>
       </c>
       <c r="O236" t="n">
-        <v>419</v>
+        <v>342</v>
       </c>
       <c r="R236" t="n">
-        <v>1.538908152378792</v>
+        <v>1.256101642275768</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -49218,13 +49218,13 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O262" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="R262" t="n">
-        <v>0.8759624055540047</v>
+        <v>0.8798383454015888</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -50562,13 +50562,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>89</v>
+        <v>515</v>
       </c>
       <c r="O269" t="n">
-        <v>89</v>
+        <v>515</v>
       </c>
       <c r="R269" t="n">
-        <v>0.3268802519372613</v>
+        <v>1.891498087052692</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -50721,13 +50721,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="O270" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="R270" t="n">
-        <v>1.0317093191012</v>
+        <v>1.42304733669131</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -50885,10 +50885,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="O271" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -51124,13 +51124,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>314</v>
+        <v>391</v>
       </c>
       <c r="O272" t="n">
-        <v>314</v>
+        <v>391</v>
       </c>
       <c r="R272" t="n">
-        <v>0.6085225560707025</v>
+        <v>0.75774624020269</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -51602,6 +51602,554 @@
       <c r="BC274" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>15</v>
+      </c>
+      <c r="O277" t="n">
+        <v>15</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.02906954885688069</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -51638,7 +52186,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -51721,7 +52269,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -51731,7 +52279,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -51751,7 +52299,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -51783,7 +52331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175083</v>
+        <v>175548</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -50562,13 +50562,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="O269" t="n">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="R269" t="n">
-        <v>1.891498087052692</v>
+        <v>1.865788404316053</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175548</v>
+        <v>175541</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -5871,7 +5871,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -29326,7 +29326,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -36095,7 +36095,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -49619,7 +49619,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -50721,13 +50721,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O270" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R270" t="n">
-        <v>1.42304733669131</v>
+        <v>1.440835428399951</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -50885,10 +50885,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O271" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -51269,13 +51269,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O273" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R273" t="n">
-        <v>0.2653463738693259</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -51433,10 +51433,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O274" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -51672,13 +51672,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -51836,10 +51836,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175541</v>
+        <v>175551</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -58740,13 +58740,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O325" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="R325" t="n">
-        <v>0.7654981198978582</v>
+        <v>0.7713120296692343</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -59691,13 +59691,13 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O330" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="R330" t="n">
-        <v>0.05426315786617728</v>
+        <v>0.0717048871803057</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178427</v>
+        <v>178439</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -57992,13 +57992,13 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="O317" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="R317" t="n">
-        <v>1.832733097940375</v>
+        <v>1.814369038842776</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -59342,13 +59342,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O326" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R326" t="n">
-        <v>1.529775886943158</v>
+        <v>1.5475639786518</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -59506,10 +59506,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O327" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
@@ -59745,13 +59745,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O328" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R328" t="n">
-        <v>0.7732499995930263</v>
+        <v>0.7713120296692343</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -60701,13 +60701,13 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O333" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R333" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -60865,10 +60865,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O334" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
@@ -61104,13 +61104,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="O335" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="R335" t="n">
-        <v>0.09883646611339433</v>
+        <v>0.1337199247416512</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178909</v>
+        <v>178926</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -51268,13 +51268,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O280" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="R280" t="n">
-        <v>1.531562528739753</v>
+        <v>1.524216905100713</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -57992,13 +57992,13 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="O317" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R317" t="n">
-        <v>1.814369038842776</v>
+        <v>1.803350603384217</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -59342,13 +59342,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O326" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R326" t="n">
-        <v>1.5475639786518</v>
+        <v>1.565352070360441</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -59506,10 +59506,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O327" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
@@ -59745,13 +59745,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O328" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="R328" t="n">
-        <v>0.7713120296692343</v>
+        <v>0.7674360898216501</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -59895,13 +59895,13 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O329" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R329" t="n">
-        <v>0.4068644399329664</v>
+        <v>0.4245541981909216</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
@@ -60059,10 +60059,10 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O330" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U330" t="inlineStr">
         <is>
@@ -60701,13 +60701,13 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O333" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R333" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -60865,10 +60865,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O334" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
@@ -61104,13 +61104,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="O335" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="R335" t="n">
-        <v>0.1337199247416512</v>
+        <v>0.1705413532937</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -61254,13 +61254,13 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O336" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R336" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -61418,10 +61418,10 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O337" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U337" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178926</v>
+        <v>178947</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -35860,13 +35860,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O196" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R196" t="n">
-        <v>0.3924849779879006</v>
+        <v>0.4018298584161838</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -36024,10 +36024,10 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O197" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
@@ -43119,13 +43119,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O236" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R236" t="n">
-        <v>0.457899140985884</v>
+        <v>0.4672440214141673</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -43283,10 +43283,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O237" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178947</v>
+        <v>178949</v>
       </c>
     </row>
     <row r="16">
